--- a/templates/level_iv_1_lepp_template.xlsx
+++ b/templates/level_iv_1_lepp_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pedro Martins\Downloads\Nova pasta (2)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pedro Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{897CC839-2175-450D-9C87-416ED4E0CF75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A04B46D-CB21-4321-8194-6D37548539F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FEBBECF9-6E9F-4757-88F6-083A764D6FE0}"/>
   </bookViews>
@@ -510,15 +510,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -528,57 +525,77 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -589,28 +606,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -621,60 +631,42 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="38">
+  <dxfs count="8">
     <dxf>
       <font>
         <color theme="0" tint="-0.24994659260841701"/>
@@ -726,240 +718,6 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color theme="0" tint="-0.24994659260841701"/>
       </font>
       <fill>
@@ -986,13 +744,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>190503</xdr:colOff>
+      <xdr:colOff>295775</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>45117</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>454306</xdr:colOff>
+      <xdr:colOff>454305</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>133459</xdr:rowOff>
     </xdr:to>
@@ -1017,8 +775,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4922924" y="45117"/>
-          <a:ext cx="720000" cy="720000"/>
+          <a:off x="5028196" y="45117"/>
+          <a:ext cx="614727" cy="720000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1036,7 +794,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>152368</xdr:colOff>
+      <xdr:colOff>105276</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>99652</xdr:rowOff>
     </xdr:to>
@@ -1068,7 +826,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="119310"/>
-          <a:ext cx="3060000" cy="612000"/>
+          <a:ext cx="3012908" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1472,12 +1230,12 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1502,36 +1260,36 @@
     </row>
     <row r="8" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="5" t="s">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
       <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="10"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="4"/>
       <c r="N9" s="1"/>
     </row>
     <row r="10" spans="1:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1552,94 +1310,94 @@
     </row>
     <row r="11" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
       <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="18"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="34"/>
       <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="49"/>
-      <c r="L14" s="49"/>
-      <c r="M14" s="49"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
       <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="23"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="31"/>
       <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="25"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11"/>
       <c r="D16" s="26"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="25"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="11"/>
       <c r="J16" s="26"/>
       <c r="K16" s="27"/>
       <c r="L16" s="27"/>
@@ -1648,14 +1406,14 @@
     </row>
     <row r="17" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="25"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
       <c r="D17" s="26"/>
       <c r="E17" s="27"/>
       <c r="F17" s="27"/>
       <c r="G17" s="28"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="25"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="11"/>
       <c r="J17" s="26"/>
       <c r="K17" s="27"/>
       <c r="L17" s="27"/>
@@ -1664,14 +1422,14 @@
     </row>
     <row r="18" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="25"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="11"/>
       <c r="D18" s="26"/>
       <c r="E18" s="27"/>
       <c r="F18" s="27"/>
       <c r="G18" s="28"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="25"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="11"/>
       <c r="J18" s="26"/>
       <c r="K18" s="27"/>
       <c r="L18" s="27"/>
@@ -1680,18 +1438,18 @@
     </row>
     <row r="19" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="33"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="37"/>
+      <c r="M19" s="38"/>
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1712,62 +1470,62 @@
     </row>
     <row r="21" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="18"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="34"/>
       <c r="N21" s="1"/>
     </row>
     <row r="22" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="49"/>
-      <c r="K22" s="49"/>
-      <c r="L22" s="49"/>
-      <c r="M22" s="49"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
       <c r="N22" s="1"/>
     </row>
     <row r="23" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="23"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="31"/>
       <c r="N23" s="1"/>
     </row>
     <row r="24" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="25"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="11"/>
       <c r="D24" s="26"/>
       <c r="E24" s="27"/>
       <c r="F24" s="27"/>
       <c r="G24" s="28"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="25"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="11"/>
       <c r="J24" s="26"/>
       <c r="K24" s="27"/>
       <c r="L24" s="27"/>
@@ -1776,14 +1534,14 @@
     </row>
     <row r="25" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="25"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="11"/>
       <c r="D25" s="26"/>
       <c r="E25" s="27"/>
       <c r="F25" s="27"/>
       <c r="G25" s="28"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="25"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="11"/>
       <c r="J25" s="26"/>
       <c r="K25" s="27"/>
       <c r="L25" s="27"/>
@@ -1792,14 +1550,14 @@
     </row>
     <row r="26" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="25"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="11"/>
       <c r="D26" s="26"/>
       <c r="E26" s="27"/>
       <c r="F26" s="27"/>
       <c r="G26" s="28"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="25"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="11"/>
       <c r="J26" s="26"/>
       <c r="K26" s="27"/>
       <c r="L26" s="27"/>
@@ -1808,94 +1566,94 @@
     </row>
     <row r="27" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="34"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="36"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="36"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="37"/>
+      <c r="M27" s="38"/>
       <c r="N27" s="1"/>
     </row>
     <row r="28" spans="1:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
-      <c r="B28" s="37"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="39"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="39"/>
-      <c r="M28" s="39"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
       <c r="N28" s="1"/>
     </row>
     <row r="29" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="18"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="34"/>
       <c r="N29" s="1"/>
     </row>
     <row r="30" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
-      <c r="B30" s="49"/>
-      <c r="C30" s="49"/>
-      <c r="D30" s="49"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="49"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="49"/>
-      <c r="K30" s="49"/>
-      <c r="L30" s="49"/>
-      <c r="M30" s="49"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
       <c r="N30" s="1"/>
     </row>
     <row r="31" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="21"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
-      <c r="M31" s="23"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="31"/>
       <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
-      <c r="B32" s="24"/>
-      <c r="C32" s="25"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="11"/>
       <c r="D32" s="26"/>
       <c r="E32" s="27"/>
       <c r="F32" s="27"/>
       <c r="G32" s="28"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="25"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="11"/>
       <c r="J32" s="26"/>
       <c r="K32" s="27"/>
       <c r="L32" s="27"/>
@@ -1904,14 +1662,14 @@
     </row>
     <row r="33" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
-      <c r="B33" s="24"/>
-      <c r="C33" s="25"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="11"/>
       <c r="D33" s="26"/>
       <c r="E33" s="27"/>
       <c r="F33" s="27"/>
       <c r="G33" s="28"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="25"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="11"/>
       <c r="J33" s="26"/>
       <c r="K33" s="27"/>
       <c r="L33" s="27"/>
@@ -1920,14 +1678,14 @@
     </row>
     <row r="34" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
-      <c r="B34" s="24"/>
-      <c r="C34" s="25"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="11"/>
       <c r="D34" s="26"/>
       <c r="E34" s="27"/>
       <c r="F34" s="27"/>
       <c r="G34" s="28"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="25"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="11"/>
       <c r="J34" s="26"/>
       <c r="K34" s="27"/>
       <c r="L34" s="27"/>
@@ -1936,34 +1694,34 @@
     </row>
     <row r="35" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="35"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="35"/>
-      <c r="L35" s="35"/>
-      <c r="M35" s="36"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="36"/>
+      <c r="K35" s="37"/>
+      <c r="L35" s="37"/>
+      <c r="M35" s="38"/>
       <c r="N35" s="1"/>
     </row>
     <row r="36" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
+      <c r="J36" s="47"/>
+      <c r="K36" s="47"/>
+      <c r="L36" s="47"/>
+      <c r="M36" s="47"/>
       <c r="N36" s="1"/>
     </row>
     <row r="37" spans="1:14" ht="16.5" x14ac:dyDescent="0.3">
@@ -1972,12 +1730,12 @@
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
-      <c r="F37" s="40" t="s">
+      <c r="F37" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="G37" s="41"/>
-      <c r="H37" s="41"/>
-      <c r="I37" s="42"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="19"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -1990,10 +1748,10 @@
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="44"/>
-      <c r="H38" s="44"/>
-      <c r="I38" s="45"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="22"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -2006,10 +1764,10 @@
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="44"/>
-      <c r="H39" s="44"/>
-      <c r="I39" s="45"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="22"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
@@ -2022,10 +1780,10 @@
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
-      <c r="F40" s="46"/>
-      <c r="G40" s="47"/>
-      <c r="H40" s="47"/>
-      <c r="I40" s="48"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="25"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
@@ -2178,23 +1936,26 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="F38:I40"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="B29:M29"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="E8:J8"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="B13:M13"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="B21:M21"/>
     <mergeCell ref="B30:G30"/>
     <mergeCell ref="H30:M30"/>
     <mergeCell ref="D23:G23"/>
@@ -2203,56 +1964,53 @@
     <mergeCell ref="J24:M24"/>
     <mergeCell ref="D25:G25"/>
     <mergeCell ref="J25:M25"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="J18:M18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="B21:M21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="E8:J8"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="B13:M13"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="B29:M29"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="F38:I40"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="J35:M35"/>
   </mergeCells>
   <conditionalFormatting sqref="D15 J15 D23 J23 D31 J31">
-    <cfRule type="cellIs" dxfId="37" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="34" operator="equal">
       <formula>"CE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16 J16 D24 J24 D32 J32">
-    <cfRule type="cellIs" dxfId="36" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="33" operator="equal">
       <formula>"MP"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9">
-    <cfRule type="cellIs" dxfId="23" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="32" operator="equal">
       <formula>"-- Tipo EAE --"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="35" operator="equal">
       <formula>"Nível IV - EXTREMO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="36" operator="equal">
       <formula>"Nível III - MUITO ELEVADO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="37" operator="equal">
       <formula>"Nível II - ELEVEADO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="38" operator="equal">
       <formula>"Nível I - MODERADO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
-    <cfRule type="cellIs" dxfId="18" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="19" operator="equal">
       <formula>"-- LEPP --"</formula>
     </cfRule>
   </conditionalFormatting>
